--- a/data/trans_camb/P6903-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P6903-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-27,15; 41,35</t>
+          <t>-25,26; 43,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,16; 35,94</t>
+          <t>-21,79; 35,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-42,47; 70,47</t>
+          <t>-42,95; 68,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-27,21; 49,92</t>
+          <t>-26,04; 45,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 57,83</t>
+          <t>-14,59; 55,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,17; 49,96</t>
+          <t>-23,16; 50,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-17,9; 32,14</t>
+          <t>-14,84; 34,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 32,47</t>
+          <t>-8,48; 33,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-24,76; 34,71</t>
+          <t>-21,1; 37,44</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-64,98; 150,69</t>
+          <t>-59,16; 181,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-46,01; 134,67</t>
+          <t>-46,37; 132,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 229,42</t>
+          <t>-100,0; 226,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-66,78; 309,15</t>
+          <t>-67,0; 267,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,17; 388,62</t>
+          <t>-37,39; 394,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-71,4; 310,32</t>
+          <t>-62,87; 326,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-45,19; 115,93</t>
+          <t>-39,44; 120,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,11; 115,98</t>
+          <t>-21,51; 125,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-63,93; 128,77</t>
+          <t>-56,73; 134,76</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,26; 7,04</t>
+          <t>-20,59; 6,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 19,48</t>
+          <t>-12,41; 15,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 28,47</t>
+          <t>-10,29; 28,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 23,43</t>
+          <t>-6,21; 25,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 22,42</t>
+          <t>-11,57; 21,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 32,77</t>
+          <t>-3,03; 32,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 8,77</t>
+          <t>-11,96; 8,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 15,35</t>
+          <t>-7,81; 14,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 23,42</t>
+          <t>-1,86; 23,78</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-52,46; 29,98</t>
+          <t>-52,45; 19,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-26,04; 62,25</t>
+          <t>-30,68; 53,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-29,91; 97,41</t>
+          <t>-27,09; 96,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-24,44; 121,02</t>
+          <t>-22,83; 130,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,56; 111,94</t>
+          <t>-37,83; 102,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 165,67</t>
+          <t>-9,76; 160,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,34; 32,07</t>
+          <t>-33,87; 30,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,08; 57,78</t>
+          <t>-20,61; 50,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 82,32</t>
+          <t>-6,19; 83,03</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-19,95; 5,91</t>
+          <t>-20,28; 5,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 14,39</t>
+          <t>-11,45; 13,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,46; 5,03</t>
+          <t>-20,86; 5,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 21,77</t>
+          <t>-9,47; 23,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 28,75</t>
+          <t>-3,87; 28,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 21,57</t>
+          <t>-8,63; 21,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 6,74</t>
+          <t>-12,48; 7,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 15,62</t>
+          <t>-4,22; 15,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 7,33</t>
+          <t>-12,74; 6,8</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-47,92; 20,98</t>
+          <t>-49,07; 18,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-25,49; 48,63</t>
+          <t>-27,88; 44,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-49,28; 18,31</t>
+          <t>-49,28; 19,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-30,37; 93,88</t>
+          <t>-26,11; 111,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 128,73</t>
+          <t>-10,23; 128,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,25; 102,31</t>
+          <t>-21,7; 101,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-32,96; 22,72</t>
+          <t>-32,48; 25,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 51,97</t>
+          <t>-10,58; 56,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-28,33; 24,45</t>
+          <t>-31,66; 22,96</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-20,2; 5,24</t>
+          <t>-18,89; 5,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 26,49</t>
+          <t>-0,6; 26,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 23,5</t>
+          <t>-2,38; 23,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-36,15; 7,79</t>
+          <t>-38,23; 6,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 23,42</t>
+          <t>-20,12; 20,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-27,14; 17,32</t>
+          <t>-30,88; 15,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-19,79; 1,54</t>
+          <t>-18,75; 2,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 22,49</t>
+          <t>-0,16; 22,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 17,57</t>
+          <t>-8,3; 17,41</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-60,37; 25,96</t>
+          <t>-58,21; 29,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 132,39</t>
+          <t>-2,71; 136,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 118,1</t>
+          <t>-7,64; 128,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-71,05; 31,99</t>
+          <t>-73,66; 26,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,8; 96,6</t>
+          <t>-38,01; 79,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-53,59; 56,24</t>
+          <t>-57,95; 50,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-56,5; 6,9</t>
+          <t>-54,8; 8,67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,87; 92,91</t>
+          <t>-0,82; 93,92</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-26,56; 69,15</t>
+          <t>-22,09; 70,95</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-18,38; 10,78</t>
+          <t>-19,12; 10,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,87; 45,29</t>
+          <t>7,52; 44,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 31,04</t>
+          <t>1,85; 31,54</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-18,16; 44,87</t>
+          <t>-17,12; 44,07</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 45,56</t>
+          <t>-15,63; 43,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 39,73</t>
+          <t>-13,84; 37,35</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 18,85</t>
+          <t>-10,84; 18,59</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,17; 40,16</t>
+          <t>8,87; 40,68</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,28; 31,09</t>
+          <t>5,91; 30,47</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-82,81; 126,33</t>
+          <t>-85,67; 140,73</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>30,85; 541,15</t>
+          <t>17,08; 483,83</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 353,81</t>
+          <t>-2,73; 342,86</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-43,97; 482,86</t>
+          <t>-39,54; 531,06</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-38,2; 438,56</t>
+          <t>-32,75; 364,99</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 531,37</t>
+          <t>-26,02; 507,74</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-44,87; 160,7</t>
+          <t>-42,75; 140,8</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>28,94; 336,36</t>
+          <t>29,38; 320,82</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>20,8; 265,97</t>
+          <t>15,31; 252,77</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-14,13; -1,34</t>
+          <t>-13,82; -0,63</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,2; 14,16</t>
+          <t>0,34; 14,16</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 10,38</t>
+          <t>-4,45; 9,63</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 12,8</t>
+          <t>-5,52; 13,35</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,1; 19,88</t>
+          <t>1,41; 20,43</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 17,25</t>
+          <t>-3,79; 16,95</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 1,88</t>
+          <t>-8,41; 2,44</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>3,17; 14,26</t>
+          <t>3,3; 14,52</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 10,88</t>
+          <t>-2,01; 10,84</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-40,79; -4,91</t>
+          <t>-40,49; -2,09</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>0,38; 50,01</t>
+          <t>1,02; 49,35</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 35,78</t>
+          <t>-13,54; 33,1</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-15,47; 48,02</t>
+          <t>-15,07; 52,06</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>6,26; 78,9</t>
+          <t>4,13; 78,2</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 64,66</t>
+          <t>-9,18; 62,47</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-24,12; 6,57</t>
+          <t>-25,2; 8,32</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>9,51; 50,71</t>
+          <t>9,69; 49,85</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 36,91</t>
+          <t>-5,73; 37,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6903-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P6903-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-7,17</t>
+          <t>17,97</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,98</t>
+          <t>13,63</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,06</t>
+          <t>12,76</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-25,26; 43,95</t>
+          <t>-25,03; 40,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-21,79; 35,58</t>
+          <t>-21,27; 33,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-42,95; 68,93</t>
+          <t>-40,37; 61,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-26,04; 45,98</t>
+          <t>-24,54; 49,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 55,53</t>
+          <t>-12,98; 55,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,16; 50,84</t>
+          <t>-21,57; 51,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 34,01</t>
+          <t>-16,15; 34,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 33,41</t>
+          <t>-13,16; 33,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-21,1; 37,44</t>
+          <t>-19,71; 41,32</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-19,21%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>36,38%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-59,16; 181,36</t>
+          <t>-63,94; 135,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-46,37; 132,79</t>
+          <t>-53,07; 118,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 226,59</t>
+          <t>-100,0; 190,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-67,0; 267,66</t>
+          <t>-67,94; 301,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,39; 394,27</t>
+          <t>-31,21; 388,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-62,87; 326,07</t>
+          <t>-61,16; 312,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,44; 120,7</t>
+          <t>-42,49; 133,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,51; 125,82</t>
+          <t>-31,41; 119,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-56,73; 134,76</t>
+          <t>-49,18; 154,62</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,45</t>
+          <t>11,27</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,97</t>
+          <t>14,57</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10,1</t>
+          <t>12,13</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-20,59; 6,03</t>
+          <t>-20,66; 5,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 15,34</t>
+          <t>-12,22; 16,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 28,09</t>
+          <t>-8,02; 29,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 25,44</t>
+          <t>-7,04; 25,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 21,44</t>
+          <t>-10,56; 24,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 32,29</t>
+          <t>-2,2; 33,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 8,3</t>
+          <t>-11,93; 7,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 14,46</t>
+          <t>-7,03; 14,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 23,78</t>
+          <t>-1,12; 25,0</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>37,99%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-52,45; 19,83</t>
+          <t>-54,44; 19,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-30,68; 53,52</t>
+          <t>-30,83; 54,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,09; 96,15</t>
+          <t>-19,84; 101,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,83; 130,84</t>
+          <t>-21,13; 133,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,83; 102,57</t>
+          <t>-29,2; 118,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 160,21</t>
+          <t>-9,23; 166,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,87; 30,99</t>
+          <t>-32,81; 29,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,61; 50,1</t>
+          <t>-19,52; 53,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 83,03</t>
+          <t>-3,22; 97,07</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-7,99</t>
+          <t>-8,41</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,59</t>
+          <t>6,16</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,92</t>
+          <t>-2,36</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-20,28; 5,02</t>
+          <t>-20,46; 4,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 13,08</t>
+          <t>-12,13; 13,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,86; 5,46</t>
+          <t>-21,75; 5,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 23,14</t>
+          <t>-11,31; 21,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 28,45</t>
+          <t>-4,11; 27,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 21,33</t>
+          <t>-9,25; 20,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 7,54</t>
+          <t>-12,49; 7,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 15,91</t>
+          <t>-4,34; 15,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 6,8</t>
+          <t>-12,31; 7,14</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-22,26%</t>
+          <t>-23,46%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-5,6%</t>
+          <t>-6,89%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-49,07; 18,19</t>
+          <t>-49,67; 16,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-27,88; 44,79</t>
+          <t>-30,22; 47,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-49,28; 19,6</t>
+          <t>-52,31; 17,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-26,11; 111,03</t>
+          <t>-28,69; 97,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 128,76</t>
+          <t>-10,7; 119,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,7; 101,56</t>
+          <t>-23,41; 96,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-32,48; 25,9</t>
+          <t>-32,81; 28,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 56,25</t>
+          <t>-11,58; 54,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-31,66; 22,96</t>
+          <t>-31,23; 24,89</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10,26</t>
+          <t>12,11</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,53</t>
+          <t>5,87</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7,01</t>
+          <t>12,24</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-18,89; 5,85</t>
+          <t>-18,93; 6,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 26,99</t>
+          <t>-1,27; 27,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 23,7</t>
+          <t>-0,2; 24,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-38,23; 6,29</t>
+          <t>-35,25; 8,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-20,12; 20,94</t>
+          <t>-17,73; 22,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-30,88; 15,67</t>
+          <t>-11,65; 23,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-18,75; 2,0</t>
+          <t>-20,17; 1,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 22,34</t>
+          <t>-0,7; 22,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 17,41</t>
+          <t>3,09; 23,06</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-6,43%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>41,1%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-58,21; 29,62</t>
+          <t>-56,99; 33,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 136,22</t>
+          <t>-5,51; 129,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 128,28</t>
+          <t>-0,44; 114,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-73,66; 26,27</t>
+          <t>-73,49; 28,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-38,01; 79,05</t>
+          <t>-34,44; 87,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-57,95; 50,29</t>
+          <t>-21,28; 98,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-54,8; 8,67</t>
+          <t>-56,94; 7,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 93,92</t>
+          <t>-2,24; 95,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-22,09; 70,95</t>
+          <t>8,97; 99,96</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16,89</t>
+          <t>17,59</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,05</t>
+          <t>17,34</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>19,14</t>
+          <t>20,23</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 10,76</t>
+          <t>-18,61; 11,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,52; 44,31</t>
+          <t>8,54; 44,95</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,85; 31,54</t>
+          <t>1,69; 32,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-17,12; 44,07</t>
+          <t>-17,22; 45,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-15,63; 43,63</t>
+          <t>-14,51; 44,82</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,84; 37,35</t>
+          <t>-13,27; 41,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 18,59</t>
+          <t>-10,3; 19,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,87; 40,68</t>
+          <t>7,72; 40,86</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,91; 30,47</t>
+          <t>7,18; 30,52</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>100,73%</t>
+          <t>104,9%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>103,59%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-85,67; 140,73</t>
+          <t>-76,9; 145,17</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>17,08; 483,83</t>
+          <t>30,79; 511,76</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 342,86</t>
+          <t>0,4; 372,5</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-39,54; 531,06</t>
+          <t>-41,65; 508,19</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-32,75; 364,99</t>
+          <t>-33,04; 556,15</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-26,02; 507,74</t>
+          <t>-25,58; 558,1</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-42,75; 140,8</t>
+          <t>-42,45; 163,2</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>29,38; 320,82</t>
+          <t>28,49; 326,83</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>15,31; 252,77</t>
+          <t>22,91; 244,25</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2,6</t>
+          <t>4,44</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,32</t>
+          <t>11,88</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>5,37</t>
+          <t>7,84</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-13,82; -0,63</t>
+          <t>-14,03; -1,01</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,34; 14,16</t>
+          <t>-0,54; 14,48</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 9,63</t>
+          <t>-2,31; 11,95</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 13,35</t>
+          <t>-5,18; 13,04</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,41; 20,43</t>
+          <t>2,29; 20,53</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 16,95</t>
+          <t>3,75; 19,09</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 2,44</t>
+          <t>-8,02; 2,76</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>3,3; 14,52</t>
+          <t>2,87; 14,49</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 10,84</t>
+          <t>2,59; 12,66</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-40,49; -2,09</t>
+          <t>-41,26; -4,26</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1,02; 49,35</t>
+          <t>-0,78; 51,56</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 33,1</t>
+          <t>-7,2; 43,04</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 52,06</t>
+          <t>-14,61; 51,28</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>4,13; 78,2</t>
+          <t>5,88; 78,05</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 62,47</t>
+          <t>10,53; 72,19</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-25,2; 8,32</t>
+          <t>-24,26; 10,46</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>9,69; 49,85</t>
+          <t>7,59; 49,2</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 37,27</t>
+          <t>7,64; 44,38</t>
         </is>
       </c>
     </row>
